--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00882-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00882-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{273831C4-F120-4D6D-A78F-200CBB78ACDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E52CEEC6-7EC8-45D6-A3B2-5344F5A76177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{40D40785-88CC-4957-9755-BCF4803E94DA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{8B802B32-5002-467F-8D3A-A308262AF3A7}"/>
   </bookViews>
   <sheets>
     <sheet name="00882-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1519,20 +1519,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6340A26A-CC58-4492-A8EE-D7EED984844E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3021B4-E947-4866-9FAF-13DB9D65F4CC}">
   <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="Q1" s="33"/>
       <c r="R1" s="25"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1590,7 +1590,7 @@
       <c r="Q2" s="35"/>
       <c r="R2" s="36"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1686,7 +1686,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="40">
         <v>2026</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
       <c r="B6" s="43"/>
       <c r="C6" s="45"/>
@@ -1766,7 +1766,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="50">
         <v>2025</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="52">
         <v>2024</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="50">
         <v>2023</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="52">
         <v>2022</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="50">
         <v>2021</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
         <v>43</v>
       </c>
